--- a/database/excel/products_master.xlsx
+++ b/database/excel/products_master.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="931">
   <si>
     <t>id</t>
   </si>
@@ -2952,6 +2952,15 @@
   </si>
   <si>
     <t>РОМ Малибу</t>
+  </si>
+  <si>
+    <t>food/desserts/bishkotina.jpg</t>
+  </si>
+  <si>
+    <t>food/desserts/tryful.jpg</t>
+  </si>
+  <si>
+    <t>cocktails/biyalo_frape.jpg</t>
   </si>
 </sst>
 </file>
@@ -6049,6 +6058,9 @@
       <c r="L58" t="s">
         <v>24</v>
       </c>
+      <c r="M58" t="s">
+        <v>930</v>
+      </c>
       <c r="N58" t="b">
         <v>0</v>
       </c>
@@ -8223,7 +8235,9 @@
       <c r="L101" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M101" s="2"/>
+      <c r="M101" s="2" t="s">
+        <v>928</v>
+      </c>
       <c r="N101" s="2" t="b">
         <v>0</v>
       </c>
@@ -8276,7 +8290,9 @@
       <c r="L102" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="M102" s="2"/>
+      <c r="M102" s="2" t="s">
+        <v>929</v>
+      </c>
       <c r="N102" s="2" t="b">
         <v>0</v>
       </c>

--- a/database/excel/products_master.xlsx
+++ b/database/excel/products_master.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="933">
   <si>
     <t>id</t>
   </si>
@@ -381,12 +381,6 @@
   </si>
   <si>
     <t>Devin</t>
-  </si>
-  <si>
-    <t>ИЗВОРНА ВОДА ДЕВИН</t>
-  </si>
-  <si>
-    <t>Devin Spring Water</t>
   </si>
   <si>
     <t>frappe_cherno</t>
@@ -2961,6 +2955,18 @@
   </si>
   <si>
     <t>cocktails/biyalo_frape.jpg</t>
+  </si>
+  <si>
+    <t>Devin Spring Water 0,5 l</t>
+  </si>
+  <si>
+    <t>Devin Spring Water 1,5 l</t>
+  </si>
+  <si>
+    <t>Изиворна вода Девин 1,5 л</t>
+  </si>
+  <si>
+    <t>Изиворна вода Девин 0,5л</t>
   </si>
 </sst>
 </file>
@@ -3444,8 +3450,8 @@
     <col min="3" max="3" width="31.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.44140625" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.109375" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" customWidth="1"/>
     <col min="10" max="10" width="10" style="4" customWidth="1"/>
@@ -3599,7 +3605,7 @@
     </row>
     <row r="4" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -3608,10 +3614,10 @@
         <v>29</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="J4" s="9">
         <v>0.4</v>
@@ -3635,7 +3641,7 @@
     </row>
     <row r="5" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -3644,10 +3650,10 @@
         <v>29</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G5" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="J5" s="9">
         <v>0.4</v>
@@ -3671,7 +3677,7 @@
     </row>
     <row r="6" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -3680,10 +3686,10 @@
         <v>21</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G6" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="J6" s="9">
         <v>1.5</v>
@@ -3782,7 +3788,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>37</v>
@@ -3794,7 +3800,7 @@
         <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>40</v>
@@ -3830,7 +3836,7 @@
     </row>
     <row r="10" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>43</v>
@@ -3841,10 +3847,10 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -3870,12 +3876,12 @@
         <v>43</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>43</v>
@@ -3886,10 +3892,10 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>888</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>890</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -3918,7 +3924,7 @@
     </row>
     <row r="12" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>43</v>
@@ -3929,10 +3935,10 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>889</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>891</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -3961,7 +3967,7 @@
     </row>
     <row r="13" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>43</v>
@@ -3972,10 +3978,10 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -4006,7 +4012,7 @@
     </row>
     <row r="14" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>43</v>
@@ -4017,10 +4023,10 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -4298,7 +4304,7 @@
         <v>66</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>67</v>
@@ -4337,7 +4343,7 @@
         <v>69</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C21" s="21" t="s">
         <v>37</v>
@@ -4572,7 +4578,7 @@
         <v>90</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>91</v>
@@ -4611,7 +4617,7 @@
         <v>92</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C27" s="21" t="s">
         <v>37</v>
@@ -4623,7 +4629,7 @@
         <v>39</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>94</v>
@@ -4716,7 +4722,7 @@
         <v>101</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>102</v>
@@ -4767,7 +4773,7 @@
         <v>104</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>105</v>
@@ -4818,7 +4824,7 @@
         <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>108</v>
@@ -4869,7 +4875,7 @@
         <v>110</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>111</v>
@@ -4920,7 +4926,7 @@
         <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>114</v>
@@ -4971,7 +4977,7 @@
         <v>39</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>40</v>
@@ -5066,10 +5072,10 @@
         <v>120</v>
       </c>
       <c r="F36" t="s">
-        <v>121</v>
+        <v>931</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>930</v>
       </c>
       <c r="J36" s="9">
         <v>1.7</v>
@@ -5098,7 +5104,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
         <v>20</v>
@@ -5107,10 +5113,10 @@
         <v>21</v>
       </c>
       <c r="F37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J37" s="9">
         <v>1.8</v>
@@ -5137,7 +5143,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
         <v>20</v>
@@ -5146,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D38" t="s">
+        <v>125</v>
+      </c>
+      <c r="E38" t="s">
+        <v>126</v>
+      </c>
+      <c r="F38" t="s">
+        <v>832</v>
+      </c>
+      <c r="G38" t="s">
         <v>127</v>
-      </c>
-      <c r="E38" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" t="s">
-        <v>834</v>
-      </c>
-      <c r="G38" t="s">
-        <v>129</v>
       </c>
       <c r="J38" s="9">
         <v>2.2000000000000002</v>
@@ -5184,7 +5190,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B39" t="s">
         <v>20</v>
@@ -5193,16 +5199,16 @@
         <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J39" s="9">
         <v>2.2000000000000002</v>
@@ -5231,7 +5237,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B40" t="s">
         <v>20</v>
@@ -5240,16 +5246,16 @@
         <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F40" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J40" s="9">
         <v>2.2000000000000002</v>
@@ -5278,7 +5284,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B41" t="s">
         <v>20</v>
@@ -5287,16 +5293,16 @@
         <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J41" s="9">
         <v>2.2000000000000002</v>
@@ -5325,7 +5331,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B42" t="s">
         <v>20</v>
@@ -5334,16 +5340,16 @@
         <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F42" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J42" s="9">
         <v>2.2000000000000002</v>
@@ -5372,7 +5378,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
@@ -5381,16 +5387,16 @@
         <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F43" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G43" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J43" s="9">
         <v>2.2000000000000002</v>
@@ -5419,7 +5425,7 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
@@ -5428,10 +5434,10 @@
         <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G44" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="J44" s="9">
         <v>2.2999999999999998</v>
@@ -5460,7 +5466,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
@@ -5469,10 +5475,10 @@
         <v>60</v>
       </c>
       <c r="F45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G45" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J45" s="9">
         <v>2.1</v>
@@ -5501,7 +5507,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
@@ -5510,13 +5516,13 @@
         <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="F46" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G46" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="J46" s="9">
         <v>3.5</v>
@@ -5545,31 +5551,31 @@
     </row>
     <row r="47" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="I47" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="J47" s="8">
         <v>2</v>
@@ -5600,7 +5606,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
@@ -5609,10 +5615,10 @@
         <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J48" s="9">
         <v>2</v>
@@ -5639,7 +5645,7 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
@@ -5648,10 +5654,10 @@
         <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J49" s="9">
         <v>2.5</v>
@@ -5678,7 +5684,7 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B50" t="s">
         <v>20</v>
@@ -5687,16 +5693,16 @@
         <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F50" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="G50" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J50" s="9">
         <v>2</v>
@@ -5725,7 +5731,7 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
@@ -5734,16 +5740,16 @@
         <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F51" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G51" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J51" s="9">
         <v>2</v>
@@ -5772,7 +5778,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B52" t="s">
         <v>20</v>
@@ -5781,16 +5787,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" t="s">
+        <v>167</v>
+      </c>
+      <c r="F52" t="s">
+        <v>830</v>
+      </c>
+      <c r="G52" t="s">
         <v>168</v>
-      </c>
-      <c r="E52" t="s">
-        <v>169</v>
-      </c>
-      <c r="F52" t="s">
-        <v>832</v>
-      </c>
-      <c r="G52" t="s">
-        <v>170</v>
       </c>
       <c r="J52" s="9">
         <v>2</v>
@@ -5819,7 +5825,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B53" t="s">
         <v>20</v>
@@ -5828,16 +5834,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F53" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J53" s="9">
         <v>2</v>
@@ -5866,7 +5872,7 @@
     </row>
     <row r="54" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>20</v>
@@ -5875,16 +5881,16 @@
         <v>65</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>101</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -5917,7 +5923,7 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B55" t="s">
         <v>20</v>
@@ -5926,10 +5932,10 @@
         <v>21</v>
       </c>
       <c r="F55" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J55" s="9">
         <v>2.1</v>
@@ -5956,7 +5962,7 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
@@ -5965,13 +5971,13 @@
         <v>21</v>
       </c>
       <c r="D56" t="s">
+        <v>178</v>
+      </c>
+      <c r="F56" t="s">
+        <v>179</v>
+      </c>
+      <c r="G56" t="s">
         <v>180</v>
-      </c>
-      <c r="F56" t="s">
-        <v>181</v>
-      </c>
-      <c r="G56" t="s">
-        <v>182</v>
       </c>
       <c r="J56" s="9">
         <v>2.1</v>
@@ -5998,7 +6004,7 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
@@ -6007,10 +6013,10 @@
         <v>21</v>
       </c>
       <c r="F57" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G57" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J57" s="9">
         <v>2.1</v>
@@ -6037,7 +6043,7 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B58" t="s">
         <v>20</v>
@@ -6046,10 +6052,10 @@
         <v>21</v>
       </c>
       <c r="F58" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G58" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J58" s="19">
         <v>2.5</v>
@@ -6059,7 +6065,7 @@
         <v>24</v>
       </c>
       <c r="M58" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -6079,7 +6085,7 @@
     </row>
     <row r="59" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>20</v>
@@ -6088,16 +6094,16 @@
         <v>65</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -6130,7 +6136,7 @@
     </row>
     <row r="60" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>20</v>
@@ -6139,16 +6145,16 @@
         <v>65</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>101</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -6181,7 +6187,7 @@
     </row>
     <row r="61" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>20</v>
@@ -6190,16 +6196,16 @@
         <v>65</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>101</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -6232,7 +6238,7 @@
     </row>
     <row r="62" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>20</v>
@@ -6241,16 +6247,16 @@
         <v>65</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>104</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -6283,7 +6289,7 @@
     </row>
     <row r="63" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>20</v>
@@ -6292,16 +6298,16 @@
         <v>65</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -6334,7 +6340,7 @@
     </row>
     <row r="64" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>20</v>
@@ -6343,16 +6349,16 @@
         <v>65</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="G64" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -6385,7 +6391,7 @@
     </row>
     <row r="65" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>20</v>
@@ -6396,10 +6402,10 @@
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -6432,25 +6438,25 @@
     </row>
     <row r="66" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C66" s="21" t="s">
         <v>37</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -6483,7 +6489,7 @@
     </row>
     <row r="67" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>20</v>
@@ -6492,16 +6498,16 @@
         <v>65</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -6534,7 +6540,7 @@
     </row>
     <row r="68" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>20</v>
@@ -6543,16 +6549,16 @@
         <v>65</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -6585,7 +6591,7 @@
     </row>
     <row r="69" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>20</v>
@@ -6594,16 +6600,16 @@
         <v>65</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -6636,7 +6642,7 @@
     </row>
     <row r="70" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>20</v>
@@ -6645,16 +6651,16 @@
         <v>65</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -6687,7 +6693,7 @@
     </row>
     <row r="71" spans="1:19" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>20</v>
@@ -6696,16 +6702,16 @@
         <v>65</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -6738,7 +6744,7 @@
     </row>
     <row r="72" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>20</v>
@@ -6747,16 +6753,16 @@
         <v>65</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -6789,7 +6795,7 @@
     </row>
     <row r="73" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>20</v>
@@ -6804,7 +6810,7 @@
         <v>39</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>94</v>
@@ -6840,7 +6846,7 @@
     </row>
     <row r="74" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>20</v>
@@ -6849,16 +6855,16 @@
         <v>65</v>
       </c>
       <c r="D74" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -6891,7 +6897,7 @@
     </row>
     <row r="75" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>20</v>
@@ -6900,16 +6906,16 @@
         <v>65</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -6942,21 +6948,21 @@
     </row>
     <row r="76" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -6983,13 +6989,13 @@
         <v>1</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S76" s="2"/>
     </row>
     <row r="77" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>20</v>
@@ -6998,16 +7004,16 @@
         <v>65</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -7040,7 +7046,7 @@
     </row>
     <row r="78" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>20</v>
@@ -7049,16 +7055,16 @@
         <v>65</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -7091,7 +7097,7 @@
     </row>
     <row r="79" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>20</v>
@@ -7100,16 +7106,16 @@
         <v>65</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>104</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -7142,7 +7148,7 @@
     </row>
     <row r="80" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>20</v>
@@ -7153,10 +7159,10 @@
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -7189,25 +7195,25 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C81" t="s">
+        <v>262</v>
+      </c>
+      <c r="D81" t="s">
+        <v>263</v>
+      </c>
+      <c r="E81" t="s">
         <v>264</v>
       </c>
-      <c r="D81" t="s">
+      <c r="F81" t="s">
+        <v>919</v>
+      </c>
+      <c r="G81" t="s">
         <v>265</v>
-      </c>
-      <c r="E81" t="s">
-        <v>266</v>
-      </c>
-      <c r="F81" t="s">
-        <v>921</v>
-      </c>
-      <c r="G81" t="s">
-        <v>267</v>
       </c>
       <c r="J81" s="9">
         <v>2.7</v>
@@ -7231,30 +7237,30 @@
         <v>1</v>
       </c>
       <c r="R81" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C82" t="s">
+        <v>262</v>
+      </c>
+      <c r="D82" t="s">
+        <v>268</v>
+      </c>
+      <c r="E82" t="s">
         <v>264</v>
       </c>
-      <c r="D82" t="s">
-        <v>270</v>
-      </c>
-      <c r="E82" t="s">
-        <v>266</v>
-      </c>
       <c r="F82" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G82" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J82" s="9">
         <v>2.5</v>
@@ -7278,30 +7284,30 @@
         <v>1</v>
       </c>
       <c r="R82" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C83" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E83" t="s">
         <v>20</v>
       </c>
       <c r="F83" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G83" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J83" s="9">
         <v>3.1</v>
@@ -7325,30 +7331,30 @@
         <v>1</v>
       </c>
       <c r="R83" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C84" t="s">
+        <v>262</v>
+      </c>
+      <c r="D84" t="s">
+        <v>271</v>
+      </c>
+      <c r="E84" t="s">
         <v>264</v>
       </c>
-      <c r="D84" t="s">
-        <v>273</v>
-      </c>
-      <c r="E84" t="s">
-        <v>266</v>
-      </c>
       <c r="F84" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G84" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J84" s="9">
         <v>3</v>
@@ -7372,12 +7378,12 @@
         <v>1</v>
       </c>
       <c r="R84" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B85" t="s">
         <v>20</v>
@@ -7386,22 +7392,22 @@
         <v>60</v>
       </c>
       <c r="D85" t="s">
+        <v>277</v>
+      </c>
+      <c r="E85" t="s">
+        <v>276</v>
+      </c>
+      <c r="F85" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" t="s">
         <v>279</v>
       </c>
-      <c r="E85" t="s">
-        <v>278</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="H85" t="s">
         <v>280</v>
       </c>
-      <c r="G85" t="s">
+      <c r="I85" t="s">
         <v>281</v>
-      </c>
-      <c r="H85" t="s">
-        <v>282</v>
-      </c>
-      <c r="I85" t="s">
-        <v>283</v>
       </c>
       <c r="J85" s="9">
         <v>2.7</v>
@@ -7426,30 +7432,30 @@
         <v>1</v>
       </c>
       <c r="R85" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C86" t="s">
+        <v>262</v>
+      </c>
+      <c r="D86" t="s">
+        <v>284</v>
+      </c>
+      <c r="E86" t="s">
         <v>264</v>
       </c>
-      <c r="D86" t="s">
-        <v>286</v>
-      </c>
-      <c r="E86" t="s">
-        <v>266</v>
-      </c>
       <c r="F86" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G86" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J86" s="9">
         <v>3.4</v>
@@ -7473,32 +7479,32 @@
         <v>1</v>
       </c>
       <c r="R86" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="I87" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="J87" s="18">
         <v>4</v>
@@ -7523,35 +7529,35 @@
         <v>1</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="88" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H88" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="I88" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="J88" s="8">
         <v>3.3</v>
@@ -7576,33 +7582,33 @@
         <v>1</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="S88" s="2"/>
     </row>
     <row r="89" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="I89" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="J89" s="8">
         <v>3.5</v>
@@ -7627,37 +7633,37 @@
         <v>1</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="S89" s="2"/>
     </row>
     <row r="90" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B90" t="s">
         <v>20</v>
       </c>
       <c r="C90" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D90" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E90" t="s">
+        <v>308</v>
+      </c>
+      <c r="F90" t="s">
+        <v>309</v>
+      </c>
+      <c r="G90" t="s">
         <v>310</v>
       </c>
-      <c r="F90" t="s">
+      <c r="H90" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="G90" t="s">
+      <c r="I90" t="s">
         <v>312</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="I90" t="s">
-        <v>314</v>
       </c>
       <c r="J90" s="9">
         <v>3.6</v>
@@ -7669,7 +7675,7 @@
         <v>24</v>
       </c>
       <c r="M90" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N90" s="2" t="b">
         <v>1</v>
@@ -7684,36 +7690,36 @@
         <v>1</v>
       </c>
       <c r="R90" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:19" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B91" t="s">
         <v>20</v>
       </c>
       <c r="C91" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D91" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E91" t="s">
+        <v>315</v>
+      </c>
+      <c r="F91" t="s">
+        <v>316</v>
+      </c>
+      <c r="G91" t="s">
         <v>317</v>
       </c>
-      <c r="F91" t="s">
+      <c r="H91" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="G91" t="s">
+      <c r="I91" t="s">
         <v>319</v>
-      </c>
-      <c r="H91" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="I91" t="s">
-        <v>321</v>
       </c>
       <c r="J91" s="9">
         <v>3.6</v>
@@ -7725,7 +7731,7 @@
         <v>24</v>
       </c>
       <c r="M91" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N91" s="2" t="b">
         <v>1</v>
@@ -7740,36 +7746,36 @@
         <v>1</v>
       </c>
       <c r="R91" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s">
         <v>20</v>
       </c>
       <c r="C92" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D92" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E92" t="s">
+        <v>322</v>
+      </c>
+      <c r="F92" t="s">
+        <v>323</v>
+      </c>
+      <c r="G92" t="s">
         <v>324</v>
       </c>
-      <c r="F92" t="s">
+      <c r="H92" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="G92" t="s">
+      <c r="I92" t="s">
         <v>326</v>
-      </c>
-      <c r="H92" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="I92" t="s">
-        <v>328</v>
       </c>
       <c r="J92" s="9">
         <v>3.6</v>
@@ -7781,7 +7787,7 @@
         <v>24</v>
       </c>
       <c r="M92" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N92" s="2" t="b">
         <v>1</v>
@@ -7796,36 +7802,36 @@
         <v>1</v>
       </c>
       <c r="R92" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s">
         <v>20</v>
       </c>
       <c r="C93" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E93" t="s">
+        <v>329</v>
+      </c>
+      <c r="F93" t="s">
+        <v>330</v>
+      </c>
+      <c r="G93" t="s">
         <v>331</v>
       </c>
-      <c r="F93" t="s">
+      <c r="H93" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="G93" t="s">
+      <c r="I93" t="s">
         <v>333</v>
-      </c>
-      <c r="H93" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="I93" t="s">
-        <v>335</v>
       </c>
       <c r="J93" s="9">
         <v>3.6</v>
@@ -7837,7 +7843,7 @@
         <v>24</v>
       </c>
       <c r="M93" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N93" s="2" t="b">
         <v>1</v>
@@ -7852,36 +7858,36 @@
         <v>1</v>
       </c>
       <c r="R93" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B94" t="s">
         <v>20</v>
       </c>
       <c r="C94" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D94" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E94" t="s">
+        <v>336</v>
+      </c>
+      <c r="F94" t="s">
+        <v>337</v>
+      </c>
+      <c r="G94" t="s">
         <v>338</v>
       </c>
-      <c r="F94" t="s">
+      <c r="H94" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="G94" t="s">
+      <c r="I94" t="s">
         <v>340</v>
-      </c>
-      <c r="H94" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="I94" t="s">
-        <v>342</v>
       </c>
       <c r="J94" s="9">
         <v>3.6</v>
@@ -7905,36 +7911,36 @@
         <v>1</v>
       </c>
       <c r="R94" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B95" t="s">
         <v>20</v>
       </c>
       <c r="C95" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D95" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E95" t="s">
+        <v>342</v>
+      </c>
+      <c r="F95" t="s">
+        <v>343</v>
+      </c>
+      <c r="G95" t="s">
         <v>344</v>
       </c>
-      <c r="F95" t="s">
+      <c r="H95" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="G95" t="s">
+      <c r="I95" t="s">
         <v>346</v>
-      </c>
-      <c r="H95" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="I95" t="s">
-        <v>348</v>
       </c>
       <c r="J95" s="9">
         <v>3.6</v>
@@ -7958,36 +7964,36 @@
         <v>1</v>
       </c>
       <c r="R95" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B96" t="s">
         <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D96" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E96" t="s">
+        <v>348</v>
+      </c>
+      <c r="F96" t="s">
+        <v>349</v>
+      </c>
+      <c r="G96" t="s">
         <v>350</v>
       </c>
-      <c r="F96" t="s">
+      <c r="H96" s="26" t="s">
         <v>351</v>
       </c>
-      <c r="G96" t="s">
+      <c r="I96" t="s">
         <v>352</v>
-      </c>
-      <c r="H96" s="26" t="s">
-        <v>353</v>
-      </c>
-      <c r="I96" t="s">
-        <v>354</v>
       </c>
       <c r="J96" s="9">
         <v>3.6</v>
@@ -8011,12 +8017,12 @@
         <v>1</v>
       </c>
       <c r="R96" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>20</v>
@@ -8025,16 +8031,16 @@
         <v>65</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
@@ -8067,21 +8073,21 @@
     </row>
     <row r="98" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
@@ -8108,27 +8114,27 @@
         <v>1</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S98" s="2"/>
     </row>
     <row r="99" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
@@ -8155,27 +8161,27 @@
         <v>1</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S99" s="2"/>
     </row>
     <row r="100" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
@@ -8202,13 +8208,13 @@
         <v>1</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="S100" s="2"/>
     </row>
     <row r="101" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>43</v>
@@ -8219,10 +8225,10 @@
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
@@ -8236,7 +8242,7 @@
         <v>57</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="N101" s="2" t="b">
         <v>0</v>
@@ -8254,12 +8260,12 @@
         <v>58</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>43</v>
@@ -8270,16 +8276,16 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H102" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="I102" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="J102" s="8">
         <v>3.5</v>
@@ -8291,7 +8297,7 @@
         <v>57</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="N102" s="2" t="b">
         <v>0</v>
@@ -8309,12 +8315,12 @@
         <v>58</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>43</v>
@@ -8325,10 +8331,10 @@
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
@@ -8342,7 +8348,7 @@
         <v>57</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="N103" s="2" t="b">
         <v>0</v>
@@ -8360,26 +8366,26 @@
         <v>58</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="104" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
@@ -8406,13 +8412,13 @@
         <v>1</v>
       </c>
       <c r="R104" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S104" s="2"/>
     </row>
     <row r="105" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>20</v>
@@ -8421,16 +8427,16 @@
         <v>65</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
@@ -8457,33 +8463,33 @@
         <v>1</v>
       </c>
       <c r="R105" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="S105" s="2"/>
     </row>
     <row r="106" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="I106" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="J106" s="8">
         <v>4</v>
@@ -8508,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="R106" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="S106" s="2">
         <v>7</v>
@@ -8516,27 +8522,27 @@
     </row>
     <row r="107" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="I107" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="J107" s="8">
         <v>4</v>
@@ -8561,33 +8567,33 @@
         <v>1</v>
       </c>
       <c r="R107" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S107" s="2"/>
     </row>
     <row r="108" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="I108" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="J108" s="8">
         <v>4.4000000000000004</v>
@@ -8612,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="R108" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S108" s="2">
         <v>1.9</v>
@@ -8620,27 +8626,27 @@
     </row>
     <row r="109" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="H109" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="I109" s="2" t="s">
         <v>898</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>900</v>
       </c>
       <c r="J109" s="8">
         <v>4</v>
@@ -8665,33 +8671,33 @@
         <v>1</v>
       </c>
       <c r="R109" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S109" s="2"/>
     </row>
     <row r="110" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="I110" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="J110" s="8">
         <v>3.6</v>
@@ -8716,33 +8722,33 @@
         <v>1</v>
       </c>
       <c r="R110" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S110" s="2"/>
     </row>
     <row r="111" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="I111" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="J111" s="8">
         <v>3.8</v>
@@ -8767,33 +8773,33 @@
         <v>1</v>
       </c>
       <c r="R111" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S111" s="2"/>
     </row>
     <row r="112" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="I112" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="J112" s="8">
         <v>3.8</v>
@@ -8818,33 +8824,33 @@
         <v>1</v>
       </c>
       <c r="R112" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S112" s="2"/>
     </row>
     <row r="113" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="I113" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="J113" s="8">
         <v>3.8</v>
@@ -8869,33 +8875,33 @@
         <v>1</v>
       </c>
       <c r="R113" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S113" s="2"/>
     </row>
     <row r="114" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="G114" s="2" t="s">
+      <c r="I114" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="J114" s="8">
         <v>3.8</v>
@@ -8920,33 +8926,33 @@
         <v>1</v>
       </c>
       <c r="R114" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S114" s="2"/>
     </row>
     <row r="115" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="I115" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="J115" s="8">
         <v>3.6</v>
@@ -8971,33 +8977,33 @@
         <v>1</v>
       </c>
       <c r="R115" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S115" s="2"/>
     </row>
     <row r="116" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="H116" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="I116" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="J116" s="8">
         <v>4</v>
@@ -9022,33 +9028,33 @@
         <v>1</v>
       </c>
       <c r="R116" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S116" s="2"/>
     </row>
     <row r="117" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="H117" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="G117" s="2" t="s">
+      <c r="I117" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="J117" s="8">
         <v>4</v>
@@ -9060,7 +9066,7 @@
         <v>24</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N117" s="2" t="b">
         <v>0</v>
@@ -9075,33 +9081,33 @@
         <v>1</v>
       </c>
       <c r="R117" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S117" s="2"/>
     </row>
     <row r="118" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="I118" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="J118" s="8">
         <v>4</v>
@@ -9113,7 +9119,7 @@
         <v>24</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="N118" s="2" t="b">
         <v>0</v>
@@ -9128,27 +9134,27 @@
         <v>1</v>
       </c>
       <c r="R118" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S118" s="2"/>
     </row>
     <row r="119" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
@@ -9175,13 +9181,13 @@
         <v>1</v>
       </c>
       <c r="R119" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S119" s="2"/>
     </row>
     <row r="120" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>43</v>
@@ -9192,16 +9198,16 @@
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H120" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="I120" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="J120" s="8">
         <v>4.5</v>
@@ -9229,32 +9235,32 @@
         <v>58</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="G121" s="2" t="s">
+      <c r="I121" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="J121" s="10">
         <v>4</v>
@@ -9279,13 +9285,13 @@
         <v>1</v>
       </c>
       <c r="R121" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S121" s="2"/>
     </row>
     <row r="122" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>43</v>
@@ -9296,16 +9302,16 @@
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H122" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="G122" s="2" t="s">
+      <c r="I122" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="J122" s="10">
         <v>3.9</v>
@@ -9317,7 +9323,7 @@
         <v>57</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N122" s="2" t="b">
         <v>0</v>
@@ -9335,26 +9341,26 @@
         <v>58</v>
       </c>
       <c r="S122" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
@@ -9381,33 +9387,33 @@
         <v>1</v>
       </c>
       <c r="R123" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S123" s="2"/>
     </row>
     <row r="124" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J124" s="8">
         <v>4.4000000000000004</v>
@@ -9419,7 +9425,7 @@
         <v>24</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="N124" s="2" t="b">
         <v>0</v>
@@ -9434,33 +9440,33 @@
         <v>1</v>
       </c>
       <c r="R124" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S124" s="2"/>
     </row>
     <row r="125" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="G125" s="2" t="s">
+      <c r="I125" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="J125" s="8">
         <v>4.4000000000000004</v>
@@ -9485,33 +9491,33 @@
         <v>1</v>
       </c>
       <c r="R125" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S125" s="2"/>
     </row>
     <row r="126" spans="1:19" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="H126" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="G126" s="2" t="s">
+      <c r="I126" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="J126" s="8">
         <v>4</v>
@@ -9536,33 +9542,33 @@
         <v>1</v>
       </c>
       <c r="R126" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S126" s="2"/>
     </row>
     <row r="127" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="H127" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="I127" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="J127" s="8">
         <v>4.5</v>
@@ -9574,7 +9580,7 @@
         <v>24</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="N127" s="2" t="b">
         <v>0</v>
@@ -9589,33 +9595,33 @@
         <v>1</v>
       </c>
       <c r="R127" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S127" s="2"/>
     </row>
     <row r="128" spans="1:19" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="G128" s="2" t="s">
+      <c r="I128" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="J128" s="8">
         <v>4</v>
@@ -9640,33 +9646,33 @@
         <v>1</v>
       </c>
       <c r="R128" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S128" s="2"/>
     </row>
     <row r="129" spans="1:19" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="I129" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="J129" s="8">
         <v>4.4000000000000004</v>
@@ -9691,33 +9697,33 @@
         <v>1</v>
       </c>
       <c r="R129" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S129" s="2"/>
     </row>
     <row r="130" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H130" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="G130" s="2" t="s">
+      <c r="I130" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="J130" s="8">
         <v>4.4000000000000004</v>
@@ -9742,33 +9748,33 @@
         <v>1</v>
       </c>
       <c r="R130" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S130" s="2"/>
     </row>
     <row r="131" spans="1:19" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="G131" s="2" t="s">
+      <c r="I131" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="I131" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="J131" s="8">
         <v>4.5</v>
@@ -9780,7 +9786,7 @@
         <v>24</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="N131" s="2" t="b">
         <v>0</v>
@@ -9795,33 +9801,33 @@
         <v>1</v>
       </c>
       <c r="R131" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S131" s="2"/>
     </row>
     <row r="132" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="G132" s="2" t="s">
+      <c r="I132" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="J132" s="8">
         <v>4.4000000000000004</v>
@@ -9846,7 +9852,7 @@
         <v>1</v>
       </c>
       <c r="R132" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S132" s="2">
         <v>7</v>
@@ -9854,27 +9860,27 @@
     </row>
     <row r="133" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="H133" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="I133" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="J133" s="8">
         <v>4.4000000000000004</v>
@@ -9897,7 +9903,7 @@
         <v>1</v>
       </c>
       <c r="R133" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="S133" s="2">
         <v>7</v>
@@ -9905,25 +9911,25 @@
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B134" t="s">
         <v>20</v>
       </c>
       <c r="C134" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D134" t="s">
+        <v>514</v>
+      </c>
+      <c r="E134" t="s">
+        <v>515</v>
+      </c>
+      <c r="F134" t="s">
+        <v>839</v>
+      </c>
+      <c r="G134" t="s">
         <v>516</v>
-      </c>
-      <c r="E134" t="s">
-        <v>517</v>
-      </c>
-      <c r="F134" t="s">
-        <v>841</v>
-      </c>
-      <c r="G134" t="s">
-        <v>518</v>
       </c>
       <c r="J134" s="9">
         <v>2.4</v>
@@ -9947,30 +9953,30 @@
         <v>1</v>
       </c>
       <c r="R134" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="135" spans="1:19" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B135" t="s">
         <v>20</v>
       </c>
       <c r="C135" t="s">
+        <v>519</v>
+      </c>
+      <c r="D135" t="s">
+        <v>520</v>
+      </c>
+      <c r="E135" t="s">
         <v>521</v>
       </c>
-      <c r="D135" t="s">
+      <c r="F135" t="s">
         <v>522</v>
       </c>
-      <c r="E135" t="s">
+      <c r="G135" t="s">
         <v>523</v>
-      </c>
-      <c r="F135" t="s">
-        <v>524</v>
-      </c>
-      <c r="G135" t="s">
-        <v>525</v>
       </c>
       <c r="J135" s="9">
         <v>3.7</v>
@@ -9994,30 +10000,30 @@
         <v>1</v>
       </c>
       <c r="R135" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B136" t="s">
         <v>20</v>
       </c>
       <c r="C136" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D136" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E136" t="s">
+        <v>525</v>
+      </c>
+      <c r="F136" t="s">
+        <v>526</v>
+      </c>
+      <c r="G136" t="s">
         <v>527</v>
-      </c>
-      <c r="F136" t="s">
-        <v>528</v>
-      </c>
-      <c r="G136" t="s">
-        <v>529</v>
       </c>
       <c r="J136" s="9">
         <v>3.7</v>
@@ -10041,30 +10047,30 @@
         <v>1</v>
       </c>
       <c r="R136" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B137" t="s">
         <v>20</v>
       </c>
       <c r="C137" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D137" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E137" t="s">
+        <v>529</v>
+      </c>
+      <c r="F137" t="s">
+        <v>530</v>
+      </c>
+      <c r="G137" t="s">
         <v>531</v>
-      </c>
-      <c r="F137" t="s">
-        <v>532</v>
-      </c>
-      <c r="G137" t="s">
-        <v>533</v>
       </c>
       <c r="J137" s="9">
         <v>3.7</v>
@@ -10088,36 +10094,36 @@
         <v>1</v>
       </c>
       <c r="R137" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="138" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>532</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C138" t="s">
+        <v>533</v>
+      </c>
+      <c r="D138" t="s">
+        <v>277</v>
+      </c>
+      <c r="E138" t="s">
+        <v>532</v>
+      </c>
+      <c r="F138" t="s">
         <v>534</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="G138" t="s">
         <v>535</v>
       </c>
-      <c r="D138" t="s">
-        <v>279</v>
-      </c>
-      <c r="E138" t="s">
-        <v>534</v>
-      </c>
-      <c r="F138" t="s">
+      <c r="H138" t="s">
         <v>536</v>
       </c>
-      <c r="G138" t="s">
+      <c r="I138" t="s">
         <v>537</v>
-      </c>
-      <c r="H138" t="s">
-        <v>538</v>
-      </c>
-      <c r="I138" t="s">
-        <v>539</v>
       </c>
       <c r="J138" s="9">
         <v>3.6</v>
@@ -10141,36 +10147,36 @@
         <v>1</v>
       </c>
       <c r="R138" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="139" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>539</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C139" t="s">
+        <v>533</v>
+      </c>
+      <c r="D139" t="s">
+        <v>277</v>
+      </c>
+      <c r="E139" t="s">
+        <v>539</v>
+      </c>
+      <c r="F139" t="s">
+        <v>540</v>
+      </c>
+      <c r="G139" t="s">
         <v>541</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C139" t="s">
-        <v>535</v>
-      </c>
-      <c r="D139" t="s">
-        <v>279</v>
-      </c>
-      <c r="E139" t="s">
-        <v>541</v>
-      </c>
-      <c r="F139" t="s">
+      <c r="H139" t="s">
         <v>542</v>
       </c>
-      <c r="G139" t="s">
+      <c r="I139" t="s">
         <v>543</v>
-      </c>
-      <c r="H139" t="s">
-        <v>544</v>
-      </c>
-      <c r="I139" t="s">
-        <v>545</v>
       </c>
       <c r="J139" s="9">
         <v>3.6</v>
@@ -10194,36 +10200,36 @@
         <v>1</v>
       </c>
       <c r="R139" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="140" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>544</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C140" t="s">
+        <v>533</v>
+      </c>
+      <c r="D140" t="s">
+        <v>277</v>
+      </c>
+      <c r="E140" t="s">
+        <v>465</v>
+      </c>
+      <c r="F140" t="s">
+        <v>923</v>
+      </c>
+      <c r="G140" t="s">
+        <v>922</v>
+      </c>
+      <c r="H140" t="s">
+        <v>545</v>
+      </c>
+      <c r="I140" t="s">
         <v>546</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C140" t="s">
-        <v>535</v>
-      </c>
-      <c r="D140" t="s">
-        <v>279</v>
-      </c>
-      <c r="E140" t="s">
-        <v>467</v>
-      </c>
-      <c r="F140" t="s">
-        <v>925</v>
-      </c>
-      <c r="G140" t="s">
-        <v>924</v>
-      </c>
-      <c r="H140" t="s">
-        <v>547</v>
-      </c>
-      <c r="I140" t="s">
-        <v>548</v>
       </c>
       <c r="J140" s="9">
         <v>3.6</v>
@@ -10247,36 +10253,36 @@
         <v>1</v>
       </c>
       <c r="R140" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="141" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>547</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C141" t="s">
+        <v>533</v>
+      </c>
+      <c r="D141" t="s">
+        <v>277</v>
+      </c>
+      <c r="E141" t="s">
+        <v>547</v>
+      </c>
+      <c r="F141" t="s">
+        <v>548</v>
+      </c>
+      <c r="G141" t="s">
         <v>549</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C141" t="s">
-        <v>535</v>
-      </c>
-      <c r="D141" t="s">
-        <v>279</v>
-      </c>
-      <c r="E141" t="s">
-        <v>549</v>
-      </c>
-      <c r="F141" t="s">
+      <c r="H141" t="s">
         <v>550</v>
       </c>
-      <c r="G141" t="s">
+      <c r="I141" t="s">
         <v>551</v>
-      </c>
-      <c r="H141" t="s">
-        <v>552</v>
-      </c>
-      <c r="I141" t="s">
-        <v>553</v>
       </c>
       <c r="J141" s="9">
         <v>4</v>
@@ -10300,36 +10306,36 @@
         <v>1</v>
       </c>
       <c r="R141" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="142" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>552</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C142" t="s">
+        <v>533</v>
+      </c>
+      <c r="D142" t="s">
+        <v>277</v>
+      </c>
+      <c r="E142" t="s">
+        <v>552</v>
+      </c>
+      <c r="F142" t="s">
+        <v>553</v>
+      </c>
+      <c r="G142" t="s">
         <v>554</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C142" t="s">
-        <v>535</v>
-      </c>
-      <c r="D142" t="s">
-        <v>279</v>
-      </c>
-      <c r="E142" t="s">
-        <v>554</v>
-      </c>
-      <c r="F142" t="s">
+      <c r="H142" t="s">
         <v>555</v>
       </c>
-      <c r="G142" t="s">
+      <c r="I142" t="s">
         <v>556</v>
-      </c>
-      <c r="H142" t="s">
-        <v>557</v>
-      </c>
-      <c r="I142" t="s">
-        <v>558</v>
       </c>
       <c r="J142" s="9">
         <v>4</v>
@@ -10353,36 +10359,36 @@
         <v>1</v>
       </c>
       <c r="R142" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="143" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>557</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C143" t="s">
+        <v>533</v>
+      </c>
+      <c r="D143" t="s">
+        <v>277</v>
+      </c>
+      <c r="E143" t="s">
+        <v>557</v>
+      </c>
+      <c r="F143" t="s">
+        <v>558</v>
+      </c>
+      <c r="G143" t="s">
         <v>559</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C143" t="s">
-        <v>535</v>
-      </c>
-      <c r="D143" t="s">
-        <v>279</v>
-      </c>
-      <c r="E143" t="s">
-        <v>559</v>
-      </c>
-      <c r="F143" t="s">
+      <c r="H143" t="s">
         <v>560</v>
       </c>
-      <c r="G143" t="s">
+      <c r="I143" t="s">
         <v>561</v>
-      </c>
-      <c r="H143" t="s">
-        <v>562</v>
-      </c>
-      <c r="I143" t="s">
-        <v>563</v>
       </c>
       <c r="J143" s="9">
         <v>3</v>
@@ -10406,36 +10412,36 @@
         <v>1</v>
       </c>
       <c r="R143" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="144" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>563</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C144" t="s">
+        <v>533</v>
+      </c>
+      <c r="D144" t="s">
+        <v>277</v>
+      </c>
+      <c r="E144" t="s">
+        <v>563</v>
+      </c>
+      <c r="F144" t="s">
+        <v>564</v>
+      </c>
+      <c r="G144" t="s">
         <v>565</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C144" t="s">
-        <v>535</v>
-      </c>
-      <c r="D144" t="s">
-        <v>279</v>
-      </c>
-      <c r="E144" t="s">
-        <v>565</v>
-      </c>
-      <c r="F144" t="s">
+      <c r="H144" t="s">
         <v>566</v>
       </c>
-      <c r="G144" t="s">
+      <c r="I144" t="s">
         <v>567</v>
-      </c>
-      <c r="H144" t="s">
-        <v>568</v>
-      </c>
-      <c r="I144" t="s">
-        <v>569</v>
       </c>
       <c r="J144" s="9">
         <v>4</v>
@@ -10459,26 +10465,26 @@
         <v>1</v>
       </c>
       <c r="R144" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="145" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
@@ -10492,7 +10498,7 @@
         <v>57</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="N145" s="2" t="b">
         <v>0</v>
@@ -10507,33 +10513,33 @@
         <v>1</v>
       </c>
       <c r="R145" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S145" s="2"/>
     </row>
     <row r="146" spans="1:19" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H146" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="G146" s="2" t="s">
+      <c r="I146" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="I146" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="J146" s="18">
         <v>4.5</v>
@@ -10545,7 +10551,7 @@
         <v>57</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="N146" s="2" t="b">
         <v>0</v>
@@ -10560,15 +10566,15 @@
         <v>1</v>
       </c>
       <c r="R146" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S146" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="147" spans="1:19" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>43</v>
@@ -10579,16 +10585,16 @@
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="H147" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="I147" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="J147" s="8">
         <v>4.0999999999999996</v>
@@ -10616,32 +10622,32 @@
         <v>58</v>
       </c>
       <c r="S147" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="148" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="H148" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="I148" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="I148" s="2" t="s">
-        <v>587</v>
       </c>
       <c r="J148" s="8">
         <v>4.2</v>
@@ -10653,7 +10659,7 @@
         <v>24</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="N148" s="2" t="b">
         <v>0</v>
@@ -10668,13 +10674,13 @@
         <v>1</v>
       </c>
       <c r="R148" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S148" s="2"/>
     </row>
     <row r="149" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>20</v>
@@ -10683,16 +10689,16 @@
         <v>65</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>66</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
@@ -10725,10 +10731,10 @@
     </row>
     <row r="150" spans="1:19" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>37</v>
@@ -10736,16 +10742,16 @@
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="H150" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="G150" s="2" t="s">
+      <c r="I150" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="H150" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="I150" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="J150" s="8">
         <v>4.4000000000000004</v>
@@ -10770,16 +10776,16 @@
         <v>1</v>
       </c>
       <c r="R150" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S150" s="2"/>
     </row>
     <row r="151" spans="1:19" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>37</v>
@@ -10787,16 +10793,16 @@
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="H151" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="G151" s="2" t="s">
+      <c r="I151" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="I151" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="J151" s="8">
         <v>4.4000000000000004</v>
@@ -10821,16 +10827,16 @@
         <v>1</v>
       </c>
       <c r="R151" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S151" s="2"/>
     </row>
     <row r="152" spans="1:19" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>37</v>
@@ -10838,16 +10844,16 @@
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="H152" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="I152" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="J152" s="8">
         <v>5</v>
@@ -10872,16 +10878,16 @@
         <v>1</v>
       </c>
       <c r="R152" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S152" s="2"/>
     </row>
     <row r="153" spans="1:19" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>37</v>
@@ -10889,16 +10895,16 @@
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="H153" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="I153" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="J153" s="8">
         <v>4.5999999999999996</v>
@@ -10923,33 +10929,33 @@
         <v>1</v>
       </c>
       <c r="R153" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="S153" s="2"/>
     </row>
     <row r="154" spans="1:19" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="H154" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="G154" s="2" t="s">
+      <c r="I154" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="I154" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="J154" s="8">
         <v>5.4</v>
@@ -10974,15 +10980,15 @@
         <v>1</v>
       </c>
       <c r="R154" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="155" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>20</v>
@@ -10991,16 +10997,16 @@
         <v>65</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>90</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
@@ -11033,21 +11039,21 @@
     </row>
     <row r="156" spans="1:19" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
@@ -11074,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="R156" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S156" s="2">
         <v>3.7</v>
@@ -11082,27 +11088,27 @@
     </row>
     <row r="157" spans="1:19" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="H157" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="I157" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="H157" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>630</v>
       </c>
       <c r="J157" s="8">
         <v>6.5</v>
@@ -11127,39 +11133,39 @@
         <v>1</v>
       </c>
       <c r="R157" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S157" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="158" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>629</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C158" t="s">
+        <v>533</v>
+      </c>
+      <c r="D158" t="s">
+        <v>277</v>
+      </c>
+      <c r="E158" t="s">
+        <v>629</v>
+      </c>
+      <c r="F158" t="s">
+        <v>630</v>
+      </c>
+      <c r="G158" t="s">
         <v>631</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C158" t="s">
-        <v>535</v>
-      </c>
-      <c r="D158" t="s">
-        <v>279</v>
-      </c>
-      <c r="E158" t="s">
-        <v>631</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="H158" t="s">
         <v>632</v>
       </c>
-      <c r="G158" t="s">
+      <c r="I158" t="s">
         <v>633</v>
-      </c>
-      <c r="H158" t="s">
-        <v>634</v>
-      </c>
-      <c r="I158" t="s">
-        <v>635</v>
       </c>
       <c r="J158" s="9">
         <v>3.8</v>
@@ -11183,36 +11189,36 @@
         <v>1</v>
       </c>
       <c r="R158" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="159" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>634</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C159" t="s">
+        <v>533</v>
+      </c>
+      <c r="D159" t="s">
+        <v>277</v>
+      </c>
+      <c r="E159" t="s">
+        <v>634</v>
+      </c>
+      <c r="F159" t="s">
+        <v>635</v>
+      </c>
+      <c r="G159" t="s">
         <v>636</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C159" t="s">
-        <v>535</v>
-      </c>
-      <c r="D159" t="s">
-        <v>279</v>
-      </c>
-      <c r="E159" t="s">
-        <v>636</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="H159" t="s">
         <v>637</v>
       </c>
-      <c r="G159" t="s">
+      <c r="I159" t="s">
         <v>638</v>
-      </c>
-      <c r="H159" t="s">
-        <v>639</v>
-      </c>
-      <c r="I159" t="s">
-        <v>640</v>
       </c>
       <c r="J159" s="9">
         <v>5</v>
@@ -11224,7 +11230,7 @@
         <v>24</v>
       </c>
       <c r="M159" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="N159" s="2" t="b">
         <v>0</v>
@@ -11239,36 +11245,36 @@
         <v>1</v>
       </c>
       <c r="R159" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="160" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>640</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C160" t="s">
+        <v>533</v>
+      </c>
+      <c r="D160" t="s">
+        <v>277</v>
+      </c>
+      <c r="E160" t="s">
+        <v>640</v>
+      </c>
+      <c r="F160" t="s">
+        <v>641</v>
+      </c>
+      <c r="G160" t="s">
         <v>642</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C160" t="s">
-        <v>535</v>
-      </c>
-      <c r="D160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E160" t="s">
-        <v>642</v>
-      </c>
-      <c r="F160" t="s">
+      <c r="H160" t="s">
         <v>643</v>
       </c>
-      <c r="G160" t="s">
+      <c r="I160" t="s">
         <v>644</v>
-      </c>
-      <c r="H160" t="s">
-        <v>645</v>
-      </c>
-      <c r="I160" t="s">
-        <v>646</v>
       </c>
       <c r="J160" s="9">
         <v>5</v>
@@ -11292,36 +11298,36 @@
         <v>1</v>
       </c>
       <c r="R160" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="161" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>645</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C161" t="s">
+        <v>533</v>
+      </c>
+      <c r="D161" t="s">
+        <v>277</v>
+      </c>
+      <c r="E161" t="s">
+        <v>645</v>
+      </c>
+      <c r="F161" t="s">
+        <v>646</v>
+      </c>
+      <c r="G161" t="s">
         <v>647</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C161" t="s">
-        <v>535</v>
-      </c>
-      <c r="D161" t="s">
-        <v>279</v>
-      </c>
-      <c r="E161" t="s">
-        <v>647</v>
-      </c>
-      <c r="F161" t="s">
+      <c r="H161" t="s">
         <v>648</v>
       </c>
-      <c r="G161" t="s">
+      <c r="I161" t="s">
         <v>649</v>
-      </c>
-      <c r="H161" t="s">
-        <v>650</v>
-      </c>
-      <c r="I161" t="s">
-        <v>651</v>
       </c>
       <c r="J161" s="9">
         <v>5</v>
@@ -11345,26 +11351,26 @@
         <v>1</v>
       </c>
       <c r="R161" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="162" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
@@ -11391,7 +11397,7 @@
         <v>1</v>
       </c>
       <c r="R162" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S162" s="2">
         <v>3.7</v>
@@ -11399,27 +11405,27 @@
     </row>
     <row r="163" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="H163" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="I163" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="H163" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="J163" s="8">
         <v>6</v>
@@ -11431,7 +11437,7 @@
         <v>57</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="N163" s="2" t="b">
         <v>0</v>
@@ -11446,35 +11452,35 @@
         <v>1</v>
       </c>
       <c r="R163" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S163" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="164" spans="1:19" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="H164" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="G164" s="2" t="s">
+      <c r="I164" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="H164" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="I164" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="J164" s="18">
         <v>8.5</v>
@@ -11486,7 +11492,7 @@
         <v>57</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="N164" s="2" t="b">
         <v>0</v>
@@ -11501,35 +11507,35 @@
         <v>1</v>
       </c>
       <c r="R164" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="S164" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="165" spans="1:19" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="H165" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="I165" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="H165" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="I165" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="J165" s="8">
         <v>7.5</v>
@@ -11541,7 +11547,7 @@
         <v>57</v>
       </c>
       <c r="M165" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="N165" s="2" t="b">
         <v>0</v>
@@ -11556,35 +11562,35 @@
         <v>1</v>
       </c>
       <c r="R165" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S165" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="166" spans="1:19" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="H166" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="G166" s="2" t="s">
+      <c r="I166" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="I166" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="J166" s="18">
         <v>6.5</v>
@@ -11596,7 +11602,7 @@
         <v>57</v>
       </c>
       <c r="M166" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="N166" s="2" t="b">
         <v>0</v>
@@ -11611,35 +11617,35 @@
         <v>1</v>
       </c>
       <c r="R166" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="S166" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="167" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="H167" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="G167" s="2" t="s">
+      <c r="I167" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="H167" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="I167" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="J167" s="8">
         <v>8</v>
@@ -11651,7 +11657,7 @@
         <v>57</v>
       </c>
       <c r="M167" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="N167" s="2" t="b">
         <v>0</v>
@@ -11666,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="R167" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S167" s="2">
         <v>7.8</v>
@@ -11674,21 +11680,21 @@
     </row>
     <row r="168" spans="1:19" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
@@ -11715,33 +11721,33 @@
         <v>1</v>
       </c>
       <c r="R168" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S168" s="2"/>
     </row>
     <row r="169" spans="1:19" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="H169" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="I169" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="H169" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="I169" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="J169" s="8">
         <v>10.5</v>
@@ -11753,7 +11759,7 @@
         <v>57</v>
       </c>
       <c r="M169" s="27" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="N169" s="2" t="b">
         <v>0</v>
@@ -11768,7 +11774,7 @@
         <v>1</v>
       </c>
       <c r="R169" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="S169" s="2">
         <v>7</v>
@@ -11776,25 +11782,25 @@
     </row>
     <row r="170" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B170" t="s">
         <v>20</v>
       </c>
       <c r="C170" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="D170" t="s">
+        <v>520</v>
+      </c>
+      <c r="E170" t="s">
         <v>521</v>
       </c>
-      <c r="D170" t="s">
-        <v>522</v>
-      </c>
-      <c r="E170" t="s">
-        <v>523</v>
-      </c>
       <c r="F170" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G170" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="J170" s="9">
         <v>13</v>
@@ -11806,7 +11812,7 @@
         <v>24</v>
       </c>
       <c r="M170" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="O170" t="b">
         <v>0</v>
@@ -11818,30 +11824,30 @@
         <v>1</v>
       </c>
       <c r="R170" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="171" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B171" t="s">
         <v>20</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D171" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E171" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F171" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G171" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="J171" s="9">
         <v>13</v>
@@ -11862,30 +11868,30 @@
         <v>1</v>
       </c>
       <c r="R171" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="172" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B172" t="s">
         <v>20</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D172" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E172" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F172" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="G172" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="J172" s="9">
         <v>13</v>
@@ -11906,24 +11912,24 @@
         <v>1</v>
       </c>
       <c r="R172" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="173" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B173" t="s">
         <v>20</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F173" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G173" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="J173" s="9">
         <v>2.4</v>
@@ -11944,12 +11950,12 @@
         <v>1</v>
       </c>
       <c r="R173" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="174" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>20</v>
@@ -11958,16 +11964,16 @@
         <v>65</v>
       </c>
       <c r="D174" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="F174" s="12" t="s">
         <v>705</v>
       </c>
-      <c r="E174" s="2" t="s">
+      <c r="G174" s="12" t="s">
         <v>706</v>
-      </c>
-      <c r="F174" s="12" t="s">
-        <v>707</v>
-      </c>
-      <c r="G174" s="12" t="s">
-        <v>708</v>
       </c>
       <c r="H174" s="12"/>
       <c r="I174" s="12"/>
@@ -11998,27 +12004,27 @@
     </row>
     <row r="175" spans="1:19" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
       <c r="F175" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="G175" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="H175" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="G175" s="12" t="s">
+      <c r="I175" s="12" t="s">
         <v>712</v>
-      </c>
-      <c r="H175" s="12" t="s">
-        <v>713</v>
-      </c>
-      <c r="I175" s="12" t="s">
-        <v>714</v>
       </c>
       <c r="J175" s="22">
         <v>3.5</v>
@@ -12030,7 +12036,7 @@
         <v>57</v>
       </c>
       <c r="M175" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="N175" s="2" t="b">
         <v>0</v>
@@ -12045,35 +12051,35 @@
         <v>1</v>
       </c>
       <c r="R175" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:19" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
       <c r="F176" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="G176" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="H176" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="G176" s="12" t="s">
+      <c r="I176" s="12" t="s">
         <v>719</v>
-      </c>
-      <c r="H176" s="12" t="s">
-        <v>720</v>
-      </c>
-      <c r="I176" s="12" t="s">
-        <v>721</v>
       </c>
       <c r="J176" s="22">
         <v>8.5</v>
@@ -12085,7 +12091,7 @@
         <v>57</v>
       </c>
       <c r="M176" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="N176" s="2" t="b">
         <v>0</v>
@@ -12100,35 +12106,35 @@
         <v>1</v>
       </c>
       <c r="R176" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S176" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="177" spans="1:19" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
       <c r="F177" s="12" t="s">
+        <v>723</v>
+      </c>
+      <c r="G177" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="H177" s="12" t="s">
         <v>725</v>
       </c>
-      <c r="G177" s="12" t="s">
+      <c r="I177" s="12" t="s">
         <v>726</v>
-      </c>
-      <c r="H177" s="12" t="s">
-        <v>727</v>
-      </c>
-      <c r="I177" s="12" t="s">
-        <v>728</v>
       </c>
       <c r="J177" s="22">
         <v>3.4</v>
@@ -12140,7 +12146,7 @@
         <v>57</v>
       </c>
       <c r="M177" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="N177" s="2" t="b">
         <v>0</v>
@@ -12155,35 +12161,35 @@
         <v>1</v>
       </c>
       <c r="R177" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S177" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:19" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
       <c r="F178" s="12" t="s">
+        <v>729</v>
+      </c>
+      <c r="G178" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="H178" s="12" t="s">
         <v>731</v>
       </c>
-      <c r="G178" s="12" t="s">
+      <c r="I178" s="12" t="s">
         <v>732</v>
-      </c>
-      <c r="H178" s="12" t="s">
-        <v>733</v>
-      </c>
-      <c r="I178" s="12" t="s">
-        <v>734</v>
       </c>
       <c r="J178" s="22">
         <v>3.1</v>
@@ -12195,7 +12201,7 @@
         <v>57</v>
       </c>
       <c r="M178" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="N178" s="2" t="b">
         <v>0</v>
@@ -12210,35 +12216,35 @@
         <v>1</v>
       </c>
       <c r="R178" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S178" s="25" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="179" spans="1:19" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
       <c r="F179" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="G179" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="H179" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="G179" s="12" t="s">
+      <c r="I179" s="12" t="s">
         <v>738</v>
-      </c>
-      <c r="H179" s="12" t="s">
-        <v>739</v>
-      </c>
-      <c r="I179" s="12" t="s">
-        <v>740</v>
       </c>
       <c r="J179" s="22">
         <v>6</v>
@@ -12250,7 +12256,7 @@
         <v>57</v>
       </c>
       <c r="M179" s="2" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="N179" s="2" t="b">
         <v>0</v>
@@ -12265,29 +12271,29 @@
         <v>1</v>
       </c>
       <c r="R179" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S179" s="25" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="180" spans="1:19" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
       <c r="F180" s="12" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G180" s="12" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="H180" s="12"/>
       <c r="I180" s="12"/>
@@ -12299,7 +12305,7 @@
         <v>57</v>
       </c>
       <c r="M180" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="N180" s="2" t="b">
         <v>0</v>
@@ -12314,35 +12320,35 @@
         <v>1</v>
       </c>
       <c r="R180" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="S180" s="25" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="181" spans="1:19" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
       <c r="F181" s="12" t="s">
+        <v>746</v>
+      </c>
+      <c r="G181" s="12" t="s">
+        <v>747</v>
+      </c>
+      <c r="H181" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="G181" s="12" t="s">
+      <c r="I181" s="12" t="s">
         <v>749</v>
-      </c>
-      <c r="H181" s="12" t="s">
-        <v>750</v>
-      </c>
-      <c r="I181" s="12" t="s">
-        <v>751</v>
       </c>
       <c r="J181" s="22">
         <v>3.5</v>
@@ -12367,13 +12373,13 @@
         <v>1</v>
       </c>
       <c r="R181" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="S181" s="2"/>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B182" t="s">
         <v>20</v>
@@ -12382,10 +12388,10 @@
         <v>21</v>
       </c>
       <c r="F182" s="13" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G182" s="13" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="H182" s="13"/>
       <c r="I182" s="13"/>
@@ -12414,7 +12420,7 @@
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B183" t="s">
         <v>20</v>
@@ -12423,10 +12429,10 @@
         <v>29</v>
       </c>
       <c r="F183" s="13" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G183" s="13" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="H183" s="13"/>
       <c r="I183" s="13"/>
@@ -12455,7 +12461,7 @@
     </row>
     <row r="184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B184" t="s">
         <v>20</v>
@@ -12464,10 +12470,10 @@
         <v>29</v>
       </c>
       <c r="F184" s="14" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G184" s="13" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H184" s="13"/>
       <c r="I184" s="13"/>
@@ -12493,7 +12499,7 @@
     </row>
     <row r="185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B185" t="s">
         <v>20</v>
@@ -12505,10 +12511,10 @@
         <v>120</v>
       </c>
       <c r="F185" s="13" t="s">
-        <v>121</v>
+        <v>932</v>
       </c>
       <c r="G185" s="13" t="s">
-        <v>122</v>
+        <v>929</v>
       </c>
       <c r="H185" s="13"/>
       <c r="I185" s="13"/>
@@ -12539,7 +12545,7 @@
     </row>
     <row r="186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B186" t="s">
         <v>20</v>
@@ -12548,10 +12554,10 @@
         <v>60</v>
       </c>
       <c r="F186" s="13" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G186" s="13" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H186" s="13"/>
       <c r="I186" s="13"/>
@@ -12601,16 +12607,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="24" t="s">
+        <v>764</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>765</v>
+      </c>
+      <c r="D1" s="24" t="s">
         <v>766</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>767</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>768</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -12618,16 +12624,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>768</v>
+      </c>
+      <c r="C2" t="s">
+        <v>769</v>
+      </c>
+      <c r="D2" t="s">
         <v>770</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>771</v>
-      </c>
-      <c r="D2" t="s">
-        <v>772</v>
-      </c>
-      <c r="E2" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -12635,16 +12641,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C3" t="s">
+        <v>773</v>
+      </c>
+      <c r="D3" t="s">
         <v>774</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>775</v>
-      </c>
-      <c r="D3" t="s">
-        <v>776</v>
-      </c>
-      <c r="E3" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -12652,16 +12658,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>776</v>
+      </c>
+      <c r="C4" t="s">
+        <v>777</v>
+      </c>
+      <c r="D4" t="s">
         <v>778</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>779</v>
-      </c>
-      <c r="D4" t="s">
-        <v>780</v>
-      </c>
-      <c r="E4" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -12669,16 +12675,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>780</v>
+      </c>
+      <c r="C5" t="s">
+        <v>781</v>
+      </c>
+      <c r="D5" t="s">
         <v>782</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>783</v>
-      </c>
-      <c r="D5" t="s">
-        <v>784</v>
-      </c>
-      <c r="E5" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -12686,16 +12692,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D6" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -12703,16 +12709,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C7" t="s">
+        <v>787</v>
+      </c>
+      <c r="D7" t="s">
         <v>788</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>789</v>
-      </c>
-      <c r="D7" t="s">
-        <v>790</v>
-      </c>
-      <c r="E7" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -12720,16 +12726,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>790</v>
+      </c>
+      <c r="C8" t="s">
+        <v>791</v>
+      </c>
+      <c r="D8" t="s">
         <v>792</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>793</v>
-      </c>
-      <c r="D8" t="s">
-        <v>794</v>
-      </c>
-      <c r="E8" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -12737,16 +12743,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>794</v>
+      </c>
+      <c r="C9" t="s">
+        <v>795</v>
+      </c>
+      <c r="D9" t="s">
         <v>796</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>797</v>
-      </c>
-      <c r="D9" t="s">
-        <v>798</v>
-      </c>
-      <c r="E9" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -12754,16 +12760,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>798</v>
+      </c>
+      <c r="C10" t="s">
+        <v>799</v>
+      </c>
+      <c r="D10" t="s">
         <v>800</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>801</v>
-      </c>
-      <c r="D10" t="s">
-        <v>802</v>
-      </c>
-      <c r="E10" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -12771,16 +12777,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>802</v>
+      </c>
+      <c r="C11" t="s">
+        <v>803</v>
+      </c>
+      <c r="D11" t="s">
         <v>804</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>805</v>
-      </c>
-      <c r="D11" t="s">
-        <v>806</v>
-      </c>
-      <c r="E11" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -12788,16 +12794,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>806</v>
+      </c>
+      <c r="C12" t="s">
+        <v>807</v>
+      </c>
+      <c r="D12" t="s">
         <v>808</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>809</v>
-      </c>
-      <c r="D12" t="s">
-        <v>810</v>
-      </c>
-      <c r="E12" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -12805,16 +12811,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>810</v>
+      </c>
+      <c r="C13" t="s">
+        <v>811</v>
+      </c>
+      <c r="D13" t="s">
         <v>812</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>813</v>
-      </c>
-      <c r="D13" t="s">
-        <v>814</v>
-      </c>
-      <c r="E13" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -12822,16 +12828,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>814</v>
+      </c>
+      <c r="C14" t="s">
+        <v>815</v>
+      </c>
+      <c r="D14" t="s">
         <v>816</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>817</v>
-      </c>
-      <c r="D14" t="s">
-        <v>818</v>
-      </c>
-      <c r="E14" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -12839,16 +12845,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>818</v>
+      </c>
+      <c r="C15" t="s">
+        <v>819</v>
+      </c>
+      <c r="D15" t="s">
         <v>820</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>821</v>
-      </c>
-      <c r="D15" t="s">
-        <v>822</v>
-      </c>
-      <c r="E15" t="s">
-        <v>823</v>
       </c>
     </row>
   </sheetData>

--- a/database/excel/products_master.xlsx
+++ b/database/excel/products_master.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S186"/>
+  <dimension ref="A1:S192"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.77734375" customWidth="1" min="1" max="1"/>
@@ -13101,6 +13101,342 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>shoferhofer_500</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>schofferhofer</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>wheat_beer</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Шьоферхофер 0,5 л</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Schöfferhofer 0,5 l</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K187" t="n">
+        <v>500</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="N187" t="b">
+        <v>0</v>
+      </c>
+      <c r="O187" t="b">
+        <v>0</v>
+      </c>
+      <c r="P187" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="b">
+        <v>1</v>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>san_migel_1000</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>san_miguel</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>lager</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Сан Мигел 1 л</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>San Miguel 1 l</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="N188" t="b">
+        <v>0</v>
+      </c>
+      <c r="O188" t="b">
+        <v>0</v>
+      </c>
+      <c r="P188" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="b">
+        <v>1</v>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>benediktiner_bure_5l</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>benediktiner</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>wheat_beer</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Бенедиктер буре 5 л</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Benediktiner keg 5 l</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>39</v>
+      </c>
+      <c r="K189" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="N189" t="b">
+        <v>0</v>
+      </c>
+      <c r="O189" t="b">
+        <v>0</v>
+      </c>
+      <c r="P189" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="b">
+        <v>1</v>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>meshana_skara_sbor</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Мешана скара</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Mixed grill</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N190" t="b">
+        <v>0</v>
+      </c>
+      <c r="O190" t="b">
+        <v>0</v>
+      </c>
+      <c r="P190" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="b">
+        <v>1</v>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>kebapche_sbor</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Кебапче</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Kebapche</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N191" t="b">
+        <v>0</v>
+      </c>
+      <c r="O191" t="b">
+        <v>0</v>
+      </c>
+      <c r="P191" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="b">
+        <v>1</v>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>kyufte_sbor</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Кюфте</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Kyufte</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N192" t="b">
+        <v>0</v>
+      </c>
+      <c r="O192" t="b">
+        <v>0</v>
+      </c>
+      <c r="P192" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="b">
+        <v>1</v>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/database/excel/products_master.xlsx
+++ b/database/excel/products_master.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S192"/>
+  <dimension ref="A1:S193"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.77734375" customWidth="1" min="1" max="1"/>
@@ -13437,6 +13437,71 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>benediktiner_500</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>benediktiner</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>wheat_beer</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Бенедиктер 0,5 л</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Benediktiner 0,5 l</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K193" t="n">
+        <v>500</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="N193" t="b">
+        <v>0</v>
+      </c>
+      <c r="O193" t="b">
+        <v>0</v>
+      </c>
+      <c r="P193" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="b">
+        <v>1</v>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S122"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/database/excel/products_master.xlsx
+++ b/database/excel/products_master.xlsx
@@ -13169,7 +13169,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>san_migel_1000</t>
+          <t>benediktiner_500</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -13184,29 +13184,29 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>san_miguel</t>
+          <t>benediktiner</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>lager</t>
+          <t>wheat_beer</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Сан Мигел 1 л</t>
+          <t>Бенедиктер 0,5 л</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>San Miguel 1 l</t>
+          <t>Benediktiner 0,5 l</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="K188" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>benediktiner_bure_5l</t>
+          <t>san_migel_1000</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13249,29 +13249,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>benediktiner</t>
+          <t>san_miguel</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>wheat_beer</t>
+          <t>lager</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Бенедиктер буре 5 л</t>
+          <t>Сан Мигел 1 л</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Benediktiner keg 5 l</t>
+          <t>San Miguel 1 l</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>39</v>
+        <v>7.4</v>
       </c>
       <c r="K189" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>meshana_skara_sbor</t>
+          <t>benediktiner_bure_5l</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -13312,18 +13312,36 @@
           <t>special_offers</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>benediktiner</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>wheat_beer</t>
+        </is>
+      </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Мешана скара</t>
+          <t>Бенедиктер буре 5 л</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Mixed grill</t>
+          <t>Benediktiner keg 5 l</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>9.5</v>
+        <v>39</v>
+      </c>
+      <c r="K190" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
       </c>
       <c r="N190" t="b">
         <v>0</v>
@@ -13339,14 +13357,14 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>alcohol</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>kebapche_sbor</t>
+          <t>meshana_skara_sbor</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -13361,16 +13379,16 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Кебапче</t>
+          <t>Мешана скара</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Kebapche</t>
+          <t>Mixed grill</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="N191" t="b">
         <v>0</v>
@@ -13393,7 +13411,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kyufte_sbor</t>
+          <t>kebapche_sbor</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -13408,12 +13426,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Кюфте</t>
+          <t>Кебапче</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Kyufte</t>
+          <t>Kebapche</t>
         </is>
       </c>
       <c r="J192" t="n">
@@ -13440,7 +13458,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>benediktiner_500</t>
+          <t>kyufte_sbor</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -13453,36 +13471,18 @@
           <t>special_offers</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>benediktiner</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>wheat_beer</t>
-        </is>
-      </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Бенедиктер 0,5 л</t>
+          <t>Кюфте</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Benediktiner 0,5 l</t>
+          <t>Kyufte</t>
         </is>
       </c>
       <c r="J193" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K193" t="n">
-        <v>500</v>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
+        <v>1.5</v>
       </c>
       <c r="N193" t="b">
         <v>0</v>
@@ -13498,7 +13498,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>food</t>
         </is>
       </c>
     </row>

--- a/database/excel/products_master.xlsx
+++ b/database/excel/products_master.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S193"/>
+  <dimension ref="A1:S194"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.77734375" customWidth="1" min="1" max="1"/>
@@ -10599,7 +10599,11 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="M150" s="2" t="n"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>cocktails/shot_pepel_ot_rozi.jpg</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="b">
         <v>0</v>
       </c>
@@ -10668,7 +10672,11 @@
           <t>ml</t>
         </is>
       </c>
-      <c r="M151" s="2" t="n"/>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>cocktails/shot_sutlyash.jpg</t>
+        </is>
+      </c>
       <c r="N151" s="2" t="b">
         <v>0</v>
       </c>
@@ -10875,7 +10883,11 @@
           <t>g</t>
         </is>
       </c>
-      <c r="M154" s="2" t="n"/>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>food/mains/tortila_s_pileshko.jpg</t>
+        </is>
+      </c>
       <c r="N154" s="2" t="b">
         <v>0</v>
       </c>
@@ -11009,7 +11021,11 @@
           <t>g</t>
         </is>
       </c>
-      <c r="M156" s="2" t="n"/>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>food/mains/topeni_sirenca.jpg</t>
+        </is>
+      </c>
       <c r="N156" s="2" t="b">
         <v>0</v>
       </c>
@@ -13234,7 +13250,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>san_migel_1000</t>
+          <t>draft_glarus_1000_sbor</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13249,26 +13265,26 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>san_miguel</t>
+          <t>nalivna_glarus</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>lager</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Сан Мигел 1 л</t>
+          <t>Наливна бира Гларус 1 л</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>San Miguel 1 l</t>
+          <t>Draft beer Glarus 1 l</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="K189" t="n">
         <v>1000</v>
@@ -13299,7 +13315,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>benediktiner_bure_5l</t>
+          <t>san_migel_1000</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -13314,29 +13330,29 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>benediktiner</t>
+          <t>san_miguel</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>wheat_beer</t>
+          <t>lager</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Бенедиктер буре 5 л</t>
+          <t>Сан Мигел 1 л</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Benediktiner keg 5 l</t>
+          <t>San Miguel 1 l</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>39</v>
+        <v>7.4</v>
       </c>
       <c r="K190" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -13364,7 +13380,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>meshana_skara_sbor</t>
+          <t>benediktiner_bure_5l</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -13377,18 +13393,36 @@
           <t>special_offers</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>benediktiner</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>wheat_beer</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Мешана скара</t>
+          <t>Бенедиктер буре 5 л</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Mixed grill</t>
+          <t>Benediktiner keg 5 l</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>9.5</v>
+        <v>39</v>
+      </c>
+      <c r="K191" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
       </c>
       <c r="N191" t="b">
         <v>0</v>
@@ -13404,14 +13438,14 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>alcohol</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>kebapche_sbor</t>
+          <t>meshana_skara_sbor</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -13426,16 +13460,16 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Кебапче</t>
+          <t>Мешана скара</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Kebapche</t>
+          <t>Mixed grill</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="N192" t="b">
         <v>0</v>
@@ -13458,7 +13492,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kyufte_sbor</t>
+          <t>kebapche_sbor</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -13473,12 +13507,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Кюфте</t>
+          <t>Кебапче</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Kyufte</t>
+          <t>Kebapche</t>
         </is>
       </c>
       <c r="J193" t="n">
@@ -13497,6 +13531,53 @@
         <v>1</v>
       </c>
       <c r="R193" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>kyufte_sbor</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>october_sbor</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>special_offers</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Кюфте</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Kyufte</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N194" t="b">
+        <v>0</v>
+      </c>
+      <c r="O194" t="b">
+        <v>0</v>
+      </c>
+      <c r="P194" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="b">
+        <v>1</v>
+      </c>
+      <c r="R194" t="inlineStr">
         <is>
           <t>food</t>
         </is>
